--- a/testData/OpenCart_LoginData.xlsx
+++ b/testData/OpenCart_LoginData.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t xml:space="preserve">Username </t>
   </si>
@@ -41,13 +41,7 @@
     <t>test@1234</t>
   </si>
   <si>
-    <t>lakshmi@yahoo.com</t>
-  </si>
-  <si>
     <t>abc123@gmail.com</t>
-  </si>
-  <si>
-    <t>Laxmi</t>
   </si>
   <si>
     <t>Lakshmi</t>
@@ -454,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.90625" customWidth="1"/>
@@ -480,73 +474,61 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1"/>
     <hyperlink ref="A3" r:id="rId2"/>
-    <hyperlink ref="A4" r:id="rId3"/>
-    <hyperlink ref="B5" r:id="rId4"/>
-    <hyperlink ref="A5" r:id="rId5"/>
+    <hyperlink ref="B4" r:id="rId3"/>
+    <hyperlink ref="A4" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>